--- a/光伏配储项目/电价数据/2026/硫都站.xlsx
+++ b/光伏配储项目/电价数据/2026/硫都站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51059</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.74412</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57101</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5818</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.50519</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.50202</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43759</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45441</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44129</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42334</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42069</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42069</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41391</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44414</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.28948</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11866</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09667000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10619</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.09293999999999999</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11649</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05058</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10142</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.13128</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.14296</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.14756</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09018999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.12998</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.07629999999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.02226</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15441</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21743</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26339</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21666</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.11488</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.009470000000000001</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14771</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27122</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.19208</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.57868</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.44496</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.5044999999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.03411</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.59956</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44911</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44817</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.43327</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56965</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45327</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6076</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.80138</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63735</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6225000000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.92772</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42366</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66592</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6349199999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7087899999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.63637</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.63617</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.63689</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60714</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46979</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.49061</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42612</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6927000000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.79355</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.29423</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.86381</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52867</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5187999999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50529</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48883</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46998</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41916</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59612</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.70257</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42949</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41522</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.16484</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.04664</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.49659</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.81109</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.01125</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.84348</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.50103</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.11374</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28228</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.38628</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.48108</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.26663</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.49259</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41509</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.5713200000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.70235</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5444600000000001</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68733</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7606900000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.76385</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.56437</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.53043</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8351499999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.51646</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.43824</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.01164</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47655</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.63136</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44594</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43942</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33468</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5421699999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5574600000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.44906</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40645</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.42899</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43962</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45655</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47384</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45626</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.45053</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.5145299999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.40997</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.41418</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20285</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.5518500000000001</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26854</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.50287</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.15098</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.30778</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.2785899999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38466</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.45145</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40809</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46329</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.44432</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.4861</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.64915</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52491</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6077</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5756100000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.58933</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4214</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48244</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.46333</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43686</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45776</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41941</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39574</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4611</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30039</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.11853</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.20452</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.17035</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.27508</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.27512</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.49788</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.44813</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.07937999999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.06920999999999999</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.15538</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.27939</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.17122</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.19303</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5203300000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.0571</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.12637</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.21391</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.23126</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.22062</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23998</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.2065</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26601</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.13673</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.25317</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.27293</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42045</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5928300000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45525</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43255</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29772</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26007</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05753</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04362</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05746</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.06024</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04425</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04533</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.05255</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04609000000000001</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.0363</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04749</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04874</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04388</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04357</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04645000000000001</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04585</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04296</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04292</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04421</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.0465</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04601</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21888</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04491</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05053</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05531</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04736</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00385</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.04407</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.16469</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.06098</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11752</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39518</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.44337</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35094</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.68537</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44605</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04690999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04611999999999999</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04611</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04611999999999999</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04383</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04355</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10304</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00204</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.0439</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04376</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04351</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04315</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04535</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0432</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04343</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04514</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04408</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04402</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.0459</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04457</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04729</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04764</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20019</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26914</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30229</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33572</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31802</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30165</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27144</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27123</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17256</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15881</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17115</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14788</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15961</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15879</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23646</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21421</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22675</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26915</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28601</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28077</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45548</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41817</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40213</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15657</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.9204</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91652</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86986</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.30009</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89447</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6328400000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19395</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87214</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54599</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33786</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03774</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53779</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79691</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53032</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7789400000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78226</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87698</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49871</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40712</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45633</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21422</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87915</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5512100000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54014</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49979</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45675</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42515</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43846</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43383</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40451</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58663</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42777</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5960700000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60211</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66479</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46894</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5803200000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87741</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6309199999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8754299999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8575700000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86256</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44132</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.48174</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29779</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41267</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45238</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41502</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35343</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.92304</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36048</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46656</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41763</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47476</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50002</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38766</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16556</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26219</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19926</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27724</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19738</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29004</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25564</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44813</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42041</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5966699999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89019</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.28821</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.10101</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6823400000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.76701</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.63137</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5671499999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44344</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49106</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43347</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43113</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40983</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49108</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42793</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42699</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44343</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.42795</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.41789</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.39542</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48774</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.50173</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.58023</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25063</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.59551</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.4660899999999999</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29917</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25656</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57429</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.45715</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.73485</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.45709</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43723</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42182</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32403</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.41834</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38681</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.24641</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.16022</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.16449</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.17138</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15277</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.15574</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.15273</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.16343</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27735</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.16254</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.19204</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.12623</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11117</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.17081</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.15471</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15945</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39693</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43753</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43425</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.43827</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43857</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39898</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34885</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.52786</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46019</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.41763</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28205</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26513</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19895</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24879</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24188</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26893</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2830299999999999</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24109</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38946</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24792</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41849</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35861</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.46393</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29646</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.28319</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.11818</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22406</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25351</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.5074</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7116</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.54525</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26037</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30437</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28631</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39472</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28518</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31772</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34957</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.44231</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.70647</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.75949</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48725</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45433</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.35343</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.42175</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26582</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14878</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28529</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28433</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25853</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21818</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26168</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27828</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29157</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14973</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43451</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.58433</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.67743</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.71013</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48602</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7436699999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.54116</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.9043099999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.47235</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48352</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48359</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43023</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35998</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49082</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.57228</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.5104300000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.51427</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42364</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40613</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41823</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38459</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41379</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41948</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44366</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55936</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49107</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.6315599999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.46958</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44561</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.53126</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4796</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40299</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6420399999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15684</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28381</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43335</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48542</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43416</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50447</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.55164</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.6278899999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.8131699999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.83189</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.6911499999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80686</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.61129</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.56725</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.9685199999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.88742</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6345599999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.72299</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.46046</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47378</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.5165700000000001</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47756</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.5028899999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41784</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.57196</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42889</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44344</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.47344</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.46305</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43577</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.46024</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43894</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.47513</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37539</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.41083</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39728</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18343</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40473</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44345</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46324</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11023</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18042</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42987</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41349</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41397</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39048</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36534</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44452</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39405</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27342</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22719</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28779</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23045</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28764</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25005</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25298</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.1398</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24895</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25104</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16953</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1812</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27193</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22863</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26296</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2333</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28426</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35012</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30559</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25402</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24085</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16555</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20379</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.21654</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01798</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00053</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03046</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10722</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01822</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03947</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01921</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04162</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03919</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04832</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04792</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02635</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02897</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.14182</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04951</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04935</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00289</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04936</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04951</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03439</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17045</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.1944</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23418</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27982</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26264</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26428</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26222</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26803</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.40509</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28163</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.13069</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.55703</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.15318</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26748</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.24457</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.23357</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26027</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.25169</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.2167</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.24253</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24451</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26682</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26762</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24753</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.27019</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27488</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.22382</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.15063</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.62619</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.61815</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.64707</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.56477</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.15634</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09226000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23519</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17252</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.11303</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.12173</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.07440999999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.10365</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.02941</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.03702</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.09404999999999999</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.17156</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02733</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.11265</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.11939</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.14142</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.0207</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.09570999999999999</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.10463</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.13769</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25549</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32346</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.009640000000000001</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.49897</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.58002</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.48572</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.47588</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44774</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14074</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27584</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27013</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.48256</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.42932</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33495</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.40105</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.6670499999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.63293</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.54792</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.40715</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26128</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.5201699999999999</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.53625</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46426</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.48007</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41662</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.49569</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41142</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.41026</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41628</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.43067</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.49317</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39574</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.42146</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.6126</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.37891</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41989</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38636</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26928</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.45979</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.43232</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43368</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5265599999999999</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.61286</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.6128899999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.44378</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.58429</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.52813</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5797</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.53004</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5732999999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.47841</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.16017</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.95825</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.63639</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.6257699999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.4716</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.41756</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.38287</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26463</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29635</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.23293</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.26372</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.14182</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16895</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06211</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.16286</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.03093</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19789</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16317</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25894</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15662</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05615</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05289</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06769</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07457</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05565</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.1695</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.14412</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.16356</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.26788</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.2523</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43164</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39724</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.40026</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.43818</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4568</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.6231</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38132</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.00112</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.48512</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38349</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.26468</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.25851</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27403</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11274</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01839</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01798</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.04455</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.16651</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.04163</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00523</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01861</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04654</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01696</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01831</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01675</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16552</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.26962</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04574</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23707</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.15918</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.25283</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48711</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41508</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.59201</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.6981499999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39592</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40942</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40478</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43328</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37489</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6386000000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44973</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25624</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.22997</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14379</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20663</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23026</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23224</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11391</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15018</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.02931</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.01114</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04740999999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04635</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04678</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.0452</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07872</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02924</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06344</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09668</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17023</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19459</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12026</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25667</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22795</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12345</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04735</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26227</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14602</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11682</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23587</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18557</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23819</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24333</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20356</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24485</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27661</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37336</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.52324</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41739</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38178</v>
       </c>
     </row>
   </sheetData>
